--- a/daily_matches/job_matches_2026-05-05.xlsx
+++ b/daily_matches/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Developer – R01564833</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57e3274f3d1a497</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant Level</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe42c0421243419</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Node.js, AI)</t>
+          <t>Intermediate DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blockskye</t>
+          <t>VideoAmp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, S3, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e43689e50f299ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d20bc9cdccd3580f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kearney Activate Data and AI Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Kearney</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka</t>
+          <t>Generative AI, RAG, LLaMA, FAISS, FastAPI, Git, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a8fdf20b62f0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=959ad6acf109df6d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure DevOps &amp; Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823773f421d7c545</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13bee48669ea94</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full-stack Software Engineer</t>
+          <t>Senior ML Operations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02aba90ad666acc</t>
+          <t>https://www.indeed.com/viewjob?jk=f27909204a728c19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Full Stack Software Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Skilled Wound Care</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8271eee98387089</t>
+          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, EC2, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91935a9ef995c27</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist – Applied AI (LLMs, SLMs &amp; Predictive Modeling)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>CenterWell</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Hugging Face, ClinicalBERT, TensorFlow, PyTorch, CI/CD, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187d49afc62b9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae62182a4a4c9ca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Consultant, Gen AI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lovelytics</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, MLflow, CI/CD, Databricks</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356741369760a727</t>
+          <t>https://www.indeed.com/viewjob?jk=8f9c0353445c21c8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Scientist – Generative AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,672 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Carol Stream, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0998fc2b9380cea3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Warehouse Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AGS - American Gaming Systems</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Duluth, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Copilot, Data Lake, CI/CD, PySpark, Kafka, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07c756220fa0439</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Reliability Data Scientist</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=441a14c0f46bf10b</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Daycos</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Norfolk, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea461d7f5d6b503</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1a67b6118a3e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Governance Focus)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a79412c6c993d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Sponsorships</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08bbec849ca3b35f</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Sponsorships</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d6725d807483095</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Sponsorships</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=411f14bb179dd08e</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Sponsorships</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0516dc25a3292b</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Viking Cruises</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, CI/CD, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ef4c591c35a727</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Machine Learning Solutions Engineer (ML + Infrastructure Focus)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Lightning AI</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5fac9c51986636</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P3 SRE and Platform Engineer - Sana Search - US Federal</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b004fef4bf37b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Newtown Square, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6de625a85f100d8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer II - International Card &amp; Risk Services</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f955b3f8d4770f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ETS</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88152ac42b3af433</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ShipperHQ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Docker, CI/CD, Git, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=668974c6e75ef6b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Digital Product Analytics</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Gap Inc.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1adb181bf743b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Digital Product Analytics</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Gap Inc.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b272b70cf4235</t>
+          <t>https://www.indeed.com/viewjob?jk=29a93e7bd86b5ebd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-05.xlsx
+++ b/daily_matches/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, LangChain, Glue, Redshift, BigQuery, Synapse, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, BigQuery, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Intermediate DevOps Engineer</t>
+          <t>Data Scientist – AI Systems</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VideoAmp</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20bc9cdccd3580f</t>
+          <t>https://www.indeed.com/viewjob?jk=43f158632234e5f2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kearney Activate Data and AI Solution Architect</t>
+          <t>Full Stack Developer-Philadelphia Hybrid candidates ONLY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kearney</t>
+          <t>Docupace Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, FAISS, FastAPI, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959ad6acf109df6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ada69184ef8107a5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Activated Insights</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, MySQL, SQL, R</t>
+          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13bee48669ea94</t>
+          <t>https://www.indeed.com/viewjob?jk=179ab2326437612f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ML Operations Engineer</t>
+          <t>Senior Software Engineer I (Frontend)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Shutterfly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Hadoop, Python, R</t>
+          <t>Copilot, S3, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27909204a728c19</t>
+          <t>https://www.indeed.com/viewjob?jk=832c242a79d7c6ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer I (Frontend)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Shutterfly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Java</t>
+          <t>Copilot, S3, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7a9601bcb03fa3d4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Full Stack .NET Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Codebridge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=09e5bb288b5f5d45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist – Applied AI (LLMs, SLMs &amp; Predictive Modeling)</t>
+          <t>Machine Learning Engineer, AI Inference Solutions (University Grad)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CenterWell</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, ClinicalBERT, TensorFlow, PyTorch, CI/CD, Databricks, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae62182a4a4c9ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9c0353445c21c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist – Generative AI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Snowflake, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a93e7bd86b5ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3b62cd979b59aa</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-05.xlsx
+++ b/daily_matches/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Glue, Redshift, BigQuery, Synapse, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, S3, Data Lake, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=1275c892f53f1ddf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Git, Snowflake, BigQuery, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering, Azure ML</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist – AI Systems</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+          <t>Redshift, BigQuery, Apache Airflow, Terraform, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f158632234e5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb71504ac8db0a87</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Developer-Philadelphia Hybrid candidates ONLY</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Docupace Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada69184ef8107a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Better Direct</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, Sentence Transformers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,147 +636,2212 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179ab2326437612f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca198b93393321b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I (Frontend)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shutterfly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, S3, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Dataflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832c242a79d7c6ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I (Frontend)</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shutterfly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, S3, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a9601bcb03fa3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ca5116c75d6992f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codebridge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09e5bb288b5f5d45</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, AI Inference Solutions (University Grad)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76153c3912d65896</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LLaMA, Gemini, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=daa379deb564c9ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cloud Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Scientist III - AI &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>onXmaps</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8376562a06cd082a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GCP AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c73ae8e4276e7d4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Python | AWS | Scalable Systems)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Technology Ventures</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dba261da2180a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c336ac6e03023ad6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14f1c39aa588c7f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Docker MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1f719b7c3985724</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cloud Service Desk Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Redapt inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Woodinville, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Azure ML, Redshift, CI/CD, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inspire11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a069c9111044ce8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Glue, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e5440d25ccf8a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Data Lake, PySpark, MongoDB</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e5de8dcc639cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (Production)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, AWS SageMaker, Docker, Kubernetes, CI/CD, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe8453ba97e5f71</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, FastAPI, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GCP AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b84cbe16e4e88ab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GCP AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1fa5997316fbc86</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / Data Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Redshift, Data Lake, Kinesis, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Docker MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a29381fb04306db</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Altom Transport, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83fcfc9537d38331</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f349ac6f4487a0ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>S3, Kinesis, CI/CD, Jenkins, Kafka, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed0527418ce2dd09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Docker MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer - Specialist</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Inspire11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, Synapse, Snowflake, Databricks, Redshift, Tableau, Power BI, SQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8693e9e5b27e8b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7140b7c7859592f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, Git, Snowflake, Redshift, Tableau, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60f509f4e5bf6ef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - News</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Glue, Kinesis, CI/CD, Git, Databricks, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CIBC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, Git, Databricks, Tableau, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a88548b765b34f1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be1ed446963db12f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5c8469d71a5d761</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Copilot, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfea202cc0179245</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GCP AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=860f873d8876739b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Flash AI</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, FastAPI, Docker, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6567ddf2ac1fc22</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Beth Israel Lahey Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Charlestown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=929fd4b1d3b3c404</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Good Inside</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3b62cd979b59aa</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Prompt Engineering, AWS SageMaker, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f19bb2712e5ded78</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Consultant, Full Stack Engineer - Digital &amp; Insights</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FTI Consulting, Inc.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e4c380f83d58545</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ML Engineering Consultant</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Inspire11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28b79399c00a1ac2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Zscaler</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be1f2f97b457b7a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer (Core Infra, US)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Workato</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d349985888c8db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, CI/CD, Databricks, PySpark, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0047f985550471d</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=983a31930871f32d</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer II, ML Platform, tvScientific</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>tvScientific</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93aa084628895c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, ML Platform, tvScientific</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>tvScientific</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4df1b7c30c895d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, MongoDB, Cassandra, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9b6c772788a05f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Senior Engineer - 90405345 - Washington DC, Philadelphia PA, Wilmington DE or Chicago IL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Amtrak</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AI Engineer, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1016785491ea0612</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Scientist - DCCA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Board of Governors of the Federal Reserve System</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d741ee440f8adfce</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=830b79c73ac7e6ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cloud Engineer III</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Availity, LLC.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b2eb0a9dfbaf75</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior GCP IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Terraform, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-05.xlsx
+++ b/daily_matches/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cornerstone LMS Support Engineer (L2/L3)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, Python</t>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c15b3244d5ea49</t>
+          <t>https://www.indeed.com/viewjob?jk=5b4b7adb82c010a9</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plymouth, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL, SQL</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1934c748325ba72</t>
+          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Terraform, Git, Databricks, Python, SQL</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9639a078ad7d520</t>
+          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgiana, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed9d79286e60144</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Acres, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f95df66cef20d27e</t>
+          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Florida City, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214779bd5be5ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Site Reliability Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Utahn, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
+          <t>AI Engineer, RAG, Pinecone, PyTorch, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d09ba508d5fd6ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Docker, CI/CD, Terraform, Python, R, Java</t>
+          <t>S3, Glue, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61aa13d2318db6d1</t>
+          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Architect- Enterprise Systems</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b074864ac3fad4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Software Development in Test (SDET III)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=6450e5336c97ec04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>AI Engineer (Generative AI / MLOps / AI Agents)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Novisync</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Azure ML, MLflow, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=38a516ad7e68df40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Automation Engineer - Global Operations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Pinecone, Git, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=24b6c8d39776f115</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Canopy Tax</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, FastAPI, Kubernetes, Terraform, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe807a1352916ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=af471adc52c88153</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Consultant - Software Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80b68432db623b</t>
+          <t>https://www.indeed.com/viewjob?jk=916ff0070c873866</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Agent Systems)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Redshift, Synapse, CI/CD, Git, Snowflake, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921858261a188129</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III- Gen AI Inferencing</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Federated Wireless</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bef925b175fde3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ab738bfa36942d46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III-Gen AI Inferencing</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Federated Wireless</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Jenkins, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e389ba60da58a722</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a2ba0cdeac06e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Octopus Eagle</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa88095166fbdb66</t>
+          <t>https://www.indeed.com/viewjob?jk=df2f71bd1ac4fde2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Data Scientist - Commercial Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, Git, MySQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f2af2f67029eec</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Researcher Hybrid</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, Git, Python, R, Scala</t>
+          <t>RAG, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d26ca433039c35</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Java, AI Agents)</t>
+          <t>Platform engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Alpian SA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kinesis, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,602 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15a7d0dc27b6fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=038476fa248cab70</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr AI Engineer</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thryv</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Git, Databricks, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Commence</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Leesburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Quicksight, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bbc9e0af89209e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer - Machine Learning</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Meltwater</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8e430f04b2a488e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer III</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LVT (LiveView Technologies)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfaad8ddbd08ea12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kinesis, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kinesis, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>via</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aacf6d94aa6b6f01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>via</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a4a42ebf3073eaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Engineer Development</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Montvale, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AKS, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59060e1983e14e14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DevOps / Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bespoke Labs</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6155e3c3b24641f4</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef859f1b8dcb985b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSafe Global</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Monroe, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>S3, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9178943dff355e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer, AI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LVT (LiveView Technologies)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc1e1c132f98b48f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NCX Engineer, AI Accelerator</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df3849e92e4bea0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alpian SA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8ea5cd4cbd1336c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d7228cb66a02eb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Developer II - DIGIT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd48d5db3c92e58</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Compliance, Data Engineering, Software Engineering, NY, Associate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=238ded2ffb1b639f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-05.xlsx
+++ b/daily_matches/job_matches_2026-05-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Skyventure Management LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Copilot, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b4b7adb82c010a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf4e196f6f8959b</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, EC2, Glue</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
+          <t>RAG, S3, Glue, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
+          <t>https://www.indeed.com/viewjob?jk=df49b0bead37c3d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Kinesis, Git, Snowflake, Databricks, Redshift</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, BigQuery, Dataflow, Jenkins, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, PyTorch, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, BigQuery, Dataflow, Jenkins, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platforms Analyst (National Geographic)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Glue, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, NoSQL, Python</t>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
+          <t>https://www.indeed.com/viewjob?jk=997a03ef180439de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>SW Engineer - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=98f73c720b589ea0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Development in Test (SDET III)</t>
+          <t>Data Scientist - Commercial Analytics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6450e5336c97ec04</t>
+          <t>https://www.indeed.com/viewjob?jk=04c8595073d2d717</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer (Generative AI / MLOps / AI Agents)</t>
+          <t>Data Scientist Intern - Graduate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Novisync</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Azure ML, MLflow, AKS, CI/CD</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a516ad7e68df40</t>
+          <t>https://www.indeed.com/viewjob?jk=b4232df366220c92</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Automation Engineer - Global Operations</t>
+          <t>Senior BI &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Imagine Worldwide</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Pinecone, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b6c8d39776f115</t>
+          <t>https://www.indeed.com/viewjob?jk=b722bd4cfefbea40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Kubernetes, Terraform, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af471adc52c88153</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=916ff0070c873866</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, CI/CD, Git, Snowflake, Redshift, Tableau, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Federated Wireless</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab738bfa36942d46</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Federated Wireless</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a2ba0cdeac06e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Data Scientist III, Customer Strategy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Zappos Family of Companies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Quicksight, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2f71bd1ac4fde2</t>
+          <t>https://www.indeed.com/viewjob?jk=da3d20d2fd59c8b7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist - Commercial Analytics</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>TensorFlow, PyTorch, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f2af2f67029eec</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alpian SA</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Athena, Data Lake, Kubernetes, CI/CD, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038476fa248cab70</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Git, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf785ee2ada3512</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Quicksight, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbc9e0af89209e2</t>
+          <t>https://www.indeed.com/viewjob?jk=441ab4f97b094845</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Machine Learning</t>
+          <t>Senior Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e430f04b2a488e</t>
+          <t>https://www.indeed.com/viewjob?jk=37a071d3f9acf5b6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Senior Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfaad8ddbd08ea12</t>
+          <t>https://www.indeed.com/viewjob?jk=63101a9b515022bb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba5d8ae36efa392</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2faaa7021e270b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist- Sr. Consultant level</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Kafka, Hadoop, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aacf6d94aa6b6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=28d9d86a3d6302e2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Risa Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4a42ebf3073eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=53bc37bf05f2917c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Engineer Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, AKS, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59060e1983e14e14</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2ad1a42d922265</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps / Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bespoke Labs</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef859f1b8dcb985b</t>
+          <t>https://www.indeed.com/viewjob?jk=df646eebb49e9747</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>E Mortgage Capital</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, AKS, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9178943dff355e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d80d00a457014d48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer, AI</t>
+          <t>AI Engineer (Internship) - Intelligent Question Bank Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Accel Learning</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Gemini, Pinecone, Prompt Engineering, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc1e1c132f98b48f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177fd0bdc7869d0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NCX Engineer, AI Accelerator</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, Kubernetes, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3849e92e4bea0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3101b6f068f94389</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alpian SA</t>
+          <t>Pinwheel</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ea5cd4cbd1336c</t>
+          <t>https://www.indeed.com/viewjob?jk=90af62880bb01bd2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer 3 (Ensign Peak Advisors)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Church of Jesus Christ of Latter-day Saints</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
+          <t>Kubernetes, GitHub Actions, Git, Snowflake, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7228cb66a02eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8cffc4307f09db2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Developer II - DIGIT</t>
+          <t>Senior Cloud Software Engineer - Intelligent Document Processing</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Danbury, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd48d5db3c92e58</t>
+          <t>https://www.indeed.com/viewjob?jk=444759dfac2c0967</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Compliance, Data Engineering, Software Engineering, NY, Associate</t>
+          <t>Senior Cloud Software Engineer - Intelligent Document Processing</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,182 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238ded2ffb1b639f</t>
+          <t>https://www.indeed.com/viewjob?jk=366bd7c1aae31719</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer - Intelligent Document Processing</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eea7dcea90396982</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer - Intelligent Document Processing</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=250fbf9243205937</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer - Intelligent Document Processing</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6521769a184bbe1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer - Intelligent Document Processing</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d1a55d8ea8238c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Scientist, AI/ML– Visa Consulting and Analytics</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43b099f8180deb7f</t>
         </is>
       </c>
     </row>
